--- a/QuestionBank.xlsx
+++ b/QuestionBank.xlsx
@@ -1353,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.28515625" customWidth="1" min="1" max="1"/>
@@ -1496,6 +1496,16 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Marks_A_UG</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Marks_B_UG</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1650,6 +1660,12 @@
           <t>Case 1 – Delayed Immunization (Catch-up Vaccination)</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1745,6 +1761,12 @@
           <t>Case 2 – IMNCI: Diarrhoea with Some Dehydration</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -1845,6 +1867,12 @@
           <t>Case 3 – IMNCI: Severe Dehydration</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" ht="105" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -1940,6 +1968,12 @@
           <t>Case 4 – IMNCI: Pneumonia</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -2038,6 +2072,12 @@
           <t>Case 5 – High-Risk Antenatal Mother</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -2133,6 +2173,12 @@
           <t>Case 6 – Delayed Breastfeeding &amp; Top Feeding</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" ht="105" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -2228,6 +2274,12 @@
           <t>Case 7 – Uncontrolled Hypertension</t>
         </is>
       </c>
+      <c r="X9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -2323,6 +2375,12 @@
           <t>Case 8 – Uncontrolled Diabetes Mellitus</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -2418,6 +2476,12 @@
           <t>Case 9 – Dog Bite (Category III)</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -2513,6 +2577,12 @@
           <t>Case 10 – Pulmonary Tuberculosis</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" ht="135" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -2608,6 +2678,12 @@
           <t>Case 11- Severe Anaemia</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" ht="135" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -2703,6 +2779,12 @@
           <t>Leprosy MDT Case</t>
         </is>
       </c>
+      <c r="X14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" ht="135" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -2798,6 +2880,12 @@
           <t>SAM NRC Case</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" ht="135" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -2893,6 +2981,12 @@
           <t>OP Poisoning Case</t>
         </is>
       </c>
+      <c r="X16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -2988,6 +3082,12 @@
           <t>Falciparum Malaria Case</t>
         </is>
       </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" ht="135" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -3083,6 +3183,12 @@
           <t>RKSK Adolescent Case</t>
         </is>
       </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -3178,6 +3284,12 @@
           <t>Stroke NCD Case</t>
         </is>
       </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" ht="105" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -3273,6 +3385,12 @@
           <t>Geriatric NPHCE Case</t>
         </is>
       </c>
+      <c r="X20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" ht="105" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -3368,6 +3486,12 @@
           <t>Scrub Typhus Case</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -3462,6 +3586,12 @@
         <is>
           <t>Silicosis Case</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -3494,7 +3624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3637,6 +3767,16 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Marks_A_UG</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Marks_B_UG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3794,6 +3934,12 @@
           <t>In a town with mid-year population of 150,000</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -3895,6 +4041,12 @@
           <t>From the given data of a town for the year 2014</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" ht="105" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -3995,6 +4147,12 @@
           <t>Data from cohort study on blood lipid profile and cardiovascular disease</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" ht="135" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -4091,6 +4249,12 @@
           <t>Data from study on helmet use and head injury following RTA</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" ht="105" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -4187,6 +4351,12 @@
           <t>The following data of an outbreak of acute gastroenteritis during birthday party</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -4284,6 +4454,12 @@
           <t>Data from case control study on HPV vaccination &amp; cervical cancer</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" ht="105" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -4385,6 +4561,12 @@
           <t>Results of a Rapid diagnostic test for pulmonary tuberculosis compared with gold standard</t>
         </is>
       </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -4481,6 +4663,12 @@
           <t>In a particular community, 120 persons in a population of 4,000 became ill</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -4582,6 +4770,12 @@
           <t>Results of a new diagnostic test for cancer compared with gold standard</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -4678,6 +4872,12 @@
           <t>Fertility Rates</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -4779,6 +4979,12 @@
           <t>Perinatal Rates</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" ht="105" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -4878,6 +5084,12 @@
         <is>
           <t>Proportional Mortality</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15" ht="105" customHeight="1">
@@ -4980,6 +5192,12 @@
           <t>RCT NNT Calculation</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" ht="105" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -5079,6 +5297,12 @@
         <is>
           <t>Epidemic Curve</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="105" customHeight="1">
@@ -5176,6 +5400,12 @@
           <t>SMR Standardization</t>
         </is>
       </c>
+      <c r="X17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" ht="105" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -5272,6 +5502,12 @@
           <t>Cross Sectional POR</t>
         </is>
       </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -5369,6 +5605,12 @@
           <t>Confounding Analysis</t>
         </is>
       </c>
+      <c r="X19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" ht="120" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -5465,6 +5707,12 @@
           <t>R0 Herd Immunity</t>
         </is>
       </c>
+      <c r="X20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" ht="135" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -5561,6 +5809,12 @@
           <t>IDSP Surveillance</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -5657,6 +5911,12 @@
           <t>Life Table Analysis</t>
         </is>
       </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" ht="225" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -5757,6 +6017,12 @@
         <is>
           <t>Malaria</t>
         </is>
+      </c>
+      <c r="X23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5770,7 +6036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5909,6 +6175,16 @@
           <t>Answer_Key_B</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Marks_A_UG</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Marks_B_UG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6068,6 +6344,12 @@
           <t>SD ≈ 1.69 g% (variance = Σf(x-mean)²/N = 852/300 = 2.84). Moderate variability; a sizeable proportion of children fall in the lower Hb range, indicating anaemia burden.</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -6167,6 +6449,12 @@
           <t>CV = (2.72/19.5)×100 ≈ 13.9% — moderate relative variability, expected given individual variation in asthma severity.</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -6266,6 +6554,12 @@
           <t>CV (11.6%) and SD (8.38) both indicate moderate variability; CV is more useful for comparing relative variability across datasets with different units/means.</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -6369,6 +6663,12 @@
           <t>Chi-square test for two proportions; assumes independent observations, expected cell counts ≥5 (met here), and a 2×2 contingency table.</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -6472,6 +6772,12 @@
           <t>Chi-square test of independence is appropriate for two categorical variables (eye colour, sex) in a contingency table.</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -6575,6 +6881,12 @@
           <t>Paired t = 12.2/(1.23/√10) ≈ 31.4, df=9; far exceeds the critical t-value (~2.26 at 5%) — statistically highly significant reduction in BP (p&lt;0.001).</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -6673,6 +6985,12 @@
           <t>Expected infant deaths = 750×(70/1,000) ≈ 53/year. An IMR of 70/1,000 is well above the current national average (~28/1,000), indicating this is a public health priority area.</t>
         </is>
       </c>
+      <c r="X9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -6776,6 +7094,12 @@
           <t>OR of 1.8 indicates a weak-to-moderate positive association — OCP users have about 1.8 times the odds of hypertension compared to non-users; clinically relevant enough to warrant BP monitoring.</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -6879,6 +7203,12 @@
           <t>Null hypothesis: cure rate is independent of sex. Chi-square test for association in a 2×2 table is appropriate.</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -6982,6 +7312,12 @@
           <t>Null hypothesis: no difference in heart-rate-increase proportion between treated and untreated groups. Alternative: a difference exists. Chi-square test statistic used.</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -7085,6 +7421,12 @@
           <t>Chi-square test of significance for two proportions; assumes independent observations and adequate expected cell counts (met here).</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -7188,6 +7530,12 @@
           <t>OR of 4.8 indicates a strong positive association — smokers have nearly 5 times the odds of lung cancer compared to non-smokers.</t>
         </is>
       </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -7291,6 +7639,12 @@
           <t>Independent (unpaired) two-sample t-test (or Z-test given large n); assumes approximately normal distribution of birth weights in each group and independent samples.</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -7394,6 +7748,12 @@
           <t>Z-test for comparing two independent means (large sample sizes); assumes approximately normal distribution and independent samples.</t>
         </is>
       </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -7497,6 +7857,12 @@
           <t>Z-test for comparing two independent means (large sample sizes); assumes independent random samples and approximately normal distribution of intake.</t>
         </is>
       </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -7600,6 +7966,12 @@
           <t>Z-test for comparing two independent proportions; requires adequately large sample sizes and independent groups (both satisfied here).</t>
         </is>
       </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -7703,6 +8075,12 @@
           <t>Z-test for two independent proportions; large samples in both groups satisfy the normal approximation assumption.</t>
         </is>
       </c>
+      <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -7805,6 +8183,12 @@
         <is>
           <t>Z-test for two independent proportions; both groups are large, satisfying the normal approximation.</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -7905,6 +8289,12 @@
           <t>Y = a + bX, where b (slope) would be positive given r=+0.78, meaning SBP increases as BMI increases; exact numeric value of b requires the standard deviations of BMI and SBP, which are not given here.</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -7993,6 +8383,12 @@
         <is>
           <t>ROC Curve Analysis</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8007,7 +8403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8144,6 +8540,16 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Marks_A_UG</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Marks_B_UG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8298,6 +8704,12 @@
         </is>
       </c>
       <c r="V3" s="2" t="n"/>
+      <c r="W3" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -8390,6 +8802,12 @@
         </is>
       </c>
       <c r="V4" s="2" t="n"/>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -8482,6 +8900,12 @@
         </is>
       </c>
       <c r="V5" s="2" t="n"/>
+      <c r="W5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -8574,6 +8998,12 @@
         </is>
       </c>
       <c r="V6" s="2" t="n"/>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -8666,6 +9096,12 @@
         </is>
       </c>
       <c r="V7" s="2" t="n"/>
+      <c r="W7" t="n">
+        <v>5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -8758,6 +9194,12 @@
         </is>
       </c>
       <c r="V8" s="2" t="n"/>
+      <c r="W8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -8850,6 +9292,12 @@
         </is>
       </c>
       <c r="V9" s="2" t="n"/>
+      <c r="W9" t="n">
+        <v>5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -8941,6 +9389,12 @@
         </is>
       </c>
       <c r="V10" s="2" t="n"/>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -9037,6 +9491,12 @@
         </is>
       </c>
       <c r="V11" s="2" t="n"/>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -9125,6 +9585,12 @@
         </is>
       </c>
       <c r="V12" s="2" t="n"/>
+      <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" ht="105" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -9219,6 +9685,12 @@
         </is>
       </c>
       <c r="V13" s="2" t="n"/>
+      <c r="W13" t="n">
+        <v>5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9307,6 +9779,12 @@
         </is>
       </c>
       <c r="V14" s="2" t="n"/>
+      <c r="W14" t="n">
+        <v>5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -9399,6 +9877,12 @@
         </is>
       </c>
       <c r="V15" s="2" t="n"/>
+      <c r="W15" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -9487,6 +9971,12 @@
         </is>
       </c>
       <c r="V16" s="2" t="n"/>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -9579,6 +10069,12 @@
         </is>
       </c>
       <c r="V17" s="2" t="n"/>
+      <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -9671,6 +10167,12 @@
         </is>
       </c>
       <c r="V18" s="2" t="n"/>
+      <c r="W18" t="n">
+        <v>5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -9759,6 +10261,12 @@
         </is>
       </c>
       <c r="V19" s="2" t="n"/>
+      <c r="W19" t="n">
+        <v>5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -9847,6 +10355,12 @@
         </is>
       </c>
       <c r="V20" s="2" t="n"/>
+      <c r="W20" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9935,6 +10449,12 @@
         </is>
       </c>
       <c r="V21" s="2" t="n"/>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -10022,6 +10542,12 @@
         </is>
       </c>
       <c r="V22" s="2" t="n"/>
+      <c r="W22" t="n">
+        <v>5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
